--- a/data/trans_camb/P19C01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C01-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,5; -0,71</t>
+          <t>-16,73; -0,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 5,33</t>
+          <t>-12,21; 5,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,64; 73,31</t>
+          <t>59,6; 73,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,13; -9,94</t>
+          <t>-27,26; -10,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 4,51</t>
+          <t>-13,55; 4,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,56; 66,1</t>
+          <t>51,51; 66,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,83; -7,76</t>
+          <t>-19,88; -7,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 2,0</t>
+          <t>-10,45; 2,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,28; 67,31</t>
+          <t>57,35; 67,61</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,79; -3,06</t>
+          <t>-52,96; -3,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,26; 22,65</t>
+          <t>-38,18; 21,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>171,08; 337,86</t>
+          <t>172,97; 335,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-65,54; -31,66</t>
+          <t>-66,82; -33,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 14,3</t>
+          <t>-33,32; 15,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>119,61; 230,49</t>
+          <t>120,92; 226,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,43; -25,66</t>
+          <t>-55,63; -25,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 6,95</t>
+          <t>-29,26; 8,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>154,14; 243,48</t>
+          <t>155,19; 246,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 6,33</t>
+          <t>-7,59; 6,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 4,12</t>
+          <t>-9,61; 4,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 17,99</t>
+          <t>3,25; 17,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 5,85</t>
+          <t>-6,96; 5,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 10,92</t>
+          <t>-2,01; 10,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 18,2</t>
+          <t>6,29; 17,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 4,3</t>
+          <t>-5,1; 4,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 5,71</t>
+          <t>-3,82; 5,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 16,25</t>
+          <t>6,4; 15,62</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 25,49</t>
+          <t>-23,04; 24,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 15,53</t>
+          <t>-29,66; 16,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,09; 68,72</t>
+          <t>9,54; 68,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 21,66</t>
+          <t>-20,45; 22,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 40,04</t>
+          <t>-6,13; 40,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,85; 69,7</t>
+          <t>18,98; 69,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 15,37</t>
+          <t>-15,52; 17,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 21,12</t>
+          <t>-11,95; 19,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,09; 59,54</t>
+          <t>20,13; 58,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 17,24</t>
+          <t>1,0; 17,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 21,41</t>
+          <t>5,41; 21,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,09; 25,34</t>
+          <t>10,23; 25,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,86; 17,7</t>
+          <t>3,15; 17,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 21,63</t>
+          <t>6,44; 21,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,51; 23,27</t>
+          <t>10,22; 23,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 15,45</t>
+          <t>5,12; 15,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,19; 19,14</t>
+          <t>8,45; 19,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,01; 22,4</t>
+          <t>11,78; 22,39</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,89; 87,19</t>
+          <t>4,86; 86,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22,47; 113,04</t>
+          <t>18,79; 108,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,35; 129,35</t>
+          <t>35,82; 130,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,71; 81,92</t>
+          <t>10,88; 85,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,92; 100,32</t>
+          <t>22,32; 102,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,87; 106,45</t>
+          <t>34,7; 111,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,35; 70,03</t>
+          <t>18,81; 69,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,4; 87,28</t>
+          <t>30,87; 88,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43,71; 102,43</t>
+          <t>43,91; 103,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 1,0</t>
+          <t>-15,02; 0,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 1,3</t>
+          <t>-14,26; 0,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 5,32</t>
+          <t>-12,61; 4,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 8,46</t>
+          <t>-6,66; 8,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,84; -1,01</t>
+          <t>-15,13; -1,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 30,24</t>
+          <t>-8,53; 30,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 3,2</t>
+          <t>-7,89; 3,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,37; -1,69</t>
+          <t>-12,36; -1,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 18,62</t>
+          <t>-7,34; 17,0</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,42; 2,99</t>
+          <t>-36,76; 2,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,45; 4,24</t>
+          <t>-34,62; 2,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 15,82</t>
+          <t>-32,07; 14,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 26,86</t>
+          <t>-17,37; 26,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,91; -2,19</t>
+          <t>-39,86; -3,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 92,37</t>
+          <t>-23,58; 97,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 9,98</t>
+          <t>-20,54; 9,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,33; -5,03</t>
+          <t>-32,51; -5,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 56,95</t>
+          <t>-19,85; 47,68</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 10,21</t>
+          <t>-10,87; 10,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,68; 35,05</t>
+          <t>13,93; 36,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40,66; 58,03</t>
+          <t>41,04; 57,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 12,75</t>
+          <t>-7,77; 14,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,21; 36,47</t>
+          <t>14,47; 35,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,6; 55,07</t>
+          <t>39,19; 53,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 8,86</t>
+          <t>-5,97; 8,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17,18; 32,48</t>
+          <t>17,64; 32,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42,54; 54,19</t>
+          <t>42,36; 54,09</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 31,36</t>
+          <t>-24,07; 30,91</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>29,42; 104,43</t>
+          <t>30,45; 108,25</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>84,89; 175,45</t>
+          <t>88,74; 174,2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 33,34</t>
+          <t>-15,67; 38,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>28,05; 97,52</t>
+          <t>29,19; 92,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,38; 150,43</t>
+          <t>77,64; 148,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 23,86</t>
+          <t>-13,49; 23,08</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>37,62; 86,51</t>
+          <t>39,2; 86,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>92,72; 148,58</t>
+          <t>90,04; 149,0</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 14,78</t>
+          <t>-2,31; 15,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5,84; 24,33</t>
+          <t>5,6; 23,89</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9,47; 27,41</t>
+          <t>9,13; 26,64</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 16,31</t>
+          <t>-1,4; 16,25</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,59; 21,56</t>
+          <t>3,99; 22,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,55; 26,91</t>
+          <t>11,34; 27,87</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,56; 13,2</t>
+          <t>0,32; 12,57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>8,05; 21,69</t>
+          <t>7,5; 20,04</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13,21; 25,14</t>
+          <t>12,83; 25,06</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 76,98</t>
+          <t>-8,19; 76,42</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>19,22; 125,17</t>
+          <t>19,37; 122,94</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>29,59; 139,68</t>
+          <t>29,76; 132,18</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 61,16</t>
+          <t>-4,06; 60,93</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13,0; 82,05</t>
+          <t>11,14; 82,31</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,41; 100,72</t>
+          <t>29,71; 107,73</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,59; 52,79</t>
+          <t>0,99; 50,94</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>24,82; 87,67</t>
+          <t>24,56; 79,11</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>41,71; 103,25</t>
+          <t>41,46; 104,02</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,93; 14,21</t>
+          <t>3,24; 14,07</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>21,52; 34,31</t>
+          <t>21,02; 33,7</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>31,32; 43,41</t>
+          <t>31,27; 43,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7,66; 19,13</t>
+          <t>8,3; 19,17</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>17,75; 29,2</t>
+          <t>16,96; 29,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 33,27</t>
+          <t>-8,2; 33,12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,01; 15,16</t>
+          <t>7,15; 14,94</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>20,91; 30,13</t>
+          <t>21,11; 29,52</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6,4; 35,63</t>
+          <t>8,48; 35,36</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>11,85; 73,12</t>
+          <t>13,09; 74,49</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>84,5; 177,3</t>
+          <t>84,96; 179,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>121,47; 228,01</t>
+          <t>121,4; 227,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26,72; 83,92</t>
+          <t>28,54; 82,0</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>61,64; 125,81</t>
+          <t>59,58; 129,06</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 135,25</t>
+          <t>-30,25; 131,82</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,25; 69,83</t>
+          <t>26,91; 67,95</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>79,55; 136,73</t>
+          <t>80,89; 135,0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>28,4; 153,52</t>
+          <t>34,89; 150,14</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-13,62; -2,53</t>
+          <t>-13,45; -2,42</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>10,03; 22,14</t>
+          <t>10,8; 22,44</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 35,11</t>
+          <t>-14,48; 34,35</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 3,97</t>
+          <t>-7,49; 2,98</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>13,63; 25,26</t>
+          <t>14,05; 24,75</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>35,5; 44,88</t>
+          <t>35,33; 45,21</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,93; -0,96</t>
+          <t>-8,45; -0,9</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>14,0; 21,72</t>
+          <t>13,73; 21,8</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,18; 37,95</t>
+          <t>2,13; 37,81</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-35,51; -7,88</t>
+          <t>-34,85; -7,33</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>27,14; 69,13</t>
+          <t>28,17; 71,13</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-36,06; 103,17</t>
+          <t>-37,97; 99,81</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 12,77</t>
+          <t>-20,16; 10,09</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>37,15; 83,19</t>
+          <t>39,41; 80,5</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>97,3; 150,81</t>
+          <t>95,06; 148,7</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-24,16; -3,0</t>
+          <t>-23,18; -2,58</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>37,82; 67,56</t>
+          <t>37,78; 67,84</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2,06; 113,73</t>
+          <t>7,74; 113,63</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,03</t>
+          <t>-2,77; 2,36</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>8,32; 13,67</t>
+          <t>8,22; 13,7</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11,73; 28,69</t>
+          <t>11,13; 28,62</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,51</t>
+          <t>0,27; 5,26</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>9,32; 14,7</t>
+          <t>9,48; 14,79</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,16; 29,07</t>
+          <t>12,99; 28,78</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,1</t>
+          <t>-0,47; 3,17</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,31</t>
+          <t>9,71; 13,25</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>16,89; 27,91</t>
+          <t>16,28; 27,45</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 7,14</t>
+          <t>-8,95; 8,31</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>26,74; 47,87</t>
+          <t>26,39; 48,5</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>38,95; 98,94</t>
+          <t>34,43; 97,93</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1,0; 18,41</t>
+          <t>0,93; 17,42</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>28,64; 48,73</t>
+          <t>28,62; 48,68</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>42,6; 94,76</t>
+          <t>42,59; 93,87</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 10,51</t>
+          <t>-1,49; 10,48</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>29,96; 44,95</t>
+          <t>30,89; 44,55</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>56,86; 92,73</t>
+          <t>53,66; 91,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C01-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66,54</t>
+          <t>64,29</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,8</t>
+          <t>58,79</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>62,56</t>
+          <t>61,45</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,73; -0,74</t>
+          <t>-17,89; -1,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 5,19</t>
+          <t>-11,92; 5,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,6; 73,37</t>
+          <t>56,98; 70,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,26; -10,3</t>
+          <t>-27,7; -9,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 4,68</t>
+          <t>-13,91; 5,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,51; 66,01</t>
+          <t>51,68; 66,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,88; -7,72</t>
+          <t>-20,21; -8,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 2,4</t>
+          <t>-9,89; 2,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,35; 67,61</t>
+          <t>56,05; 66,41</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>239,78%</t>
+          <t>231,65%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>162,48%</t>
+          <t>162,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>195,04%</t>
+          <t>191,6%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,96; -3,52</t>
+          <t>-53,1; -5,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 21,89</t>
+          <t>-37,44; 23,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>172,97; 335,1</t>
+          <t>167,9; 320,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,82; -33,74</t>
+          <t>-66,98; -29,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,32; 15,59</t>
+          <t>-34,64; 16,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>120,92; 226,57</t>
+          <t>119,81; 224,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,63; -25,59</t>
+          <t>-56,24; -27,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 8,48</t>
+          <t>-27,52; 9,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>155,19; 246,67</t>
+          <t>153,27; 241,77</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,43</t>
+          <t>10,92</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,18</t>
+          <t>12,73</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,3</t>
+          <t>11,84</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 6,61</t>
+          <t>-6,41; 6,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 4,31</t>
+          <t>-9,17; 4,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 17,83</t>
+          <t>4,54; 18,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 5,91</t>
+          <t>-6,65; 5,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 10,86</t>
+          <t>-1,91; 11,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,29; 17,8</t>
+          <t>7,34; 19,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 4,61</t>
+          <t>-5,15; 4,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 5,42</t>
+          <t>-3,64; 5,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 15,62</t>
+          <t>6,83; 16,51</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 24,97</t>
+          <t>-20,12; 24,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,66; 16,41</t>
+          <t>-28,35; 16,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,54; 68,03</t>
+          <t>13,46; 69,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 22,52</t>
+          <t>-20,35; 21,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 40,55</t>
+          <t>-6,15; 41,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,98; 69,5</t>
+          <t>22,25; 72,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 17,74</t>
+          <t>-16,35; 16,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 19,8</t>
+          <t>-10,99; 21,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,13; 58,1</t>
+          <t>20,78; 60,28</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17,95</t>
+          <t>17,33</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,65</t>
+          <t>16,43</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,24</t>
+          <t>16,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 17,11</t>
+          <t>2,15; 17,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,41; 21,63</t>
+          <t>6,68; 22,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,23; 25,77</t>
+          <t>8,98; 24,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 17,75</t>
+          <t>3,14; 17,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,44; 21,29</t>
+          <t>6,97; 21,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 23,61</t>
+          <t>9,52; 22,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 15,63</t>
+          <t>4,89; 15,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,45; 19,63</t>
+          <t>8,24; 19,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,78; 22,39</t>
+          <t>11,65; 22,25</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>68,12%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,86; 86,22</t>
+          <t>7,42; 88,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,79; 108,59</t>
+          <t>24,97; 120,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,82; 130,62</t>
+          <t>32,84; 126,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,88; 85,87</t>
+          <t>9,83; 82,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,32; 102,38</t>
+          <t>24,32; 97,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,7; 111,42</t>
+          <t>33,07; 110,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,81; 69,84</t>
+          <t>17,78; 74,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,87; 88,84</t>
+          <t>30,35; 89,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43,91; 103,97</t>
+          <t>41,72; 101,44</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,89</t>
+          <t>-4,04</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>-2,88</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>-3,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 0,76</t>
+          <t>-14,46; 1,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 0,85</t>
+          <t>-14,64; 1,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 4,85</t>
+          <t>-12,16; 5,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 8,6</t>
+          <t>-7,02; 7,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,13; -1,2</t>
+          <t>-15,78; -1,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 30,85</t>
+          <t>-9,83; 3,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 3,12</t>
+          <t>-8,7; 2,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,36; -1,47</t>
+          <t>-12,49; -1,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 17,0</t>
+          <t>-8,65; 2,68</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-10,59%</t>
+          <t>-11,0%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>-8,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>-9,55%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,76; 2,77</t>
+          <t>-35,88; 5,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 2,92</t>
+          <t>-35,45; 4,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 14,77</t>
+          <t>-30,1; 15,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 26,91</t>
+          <t>-18,21; 24,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,86; -3,64</t>
+          <t>-39,85; -3,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 97,77</t>
+          <t>-25,29; 12,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 9,18</t>
+          <t>-22,79; 8,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,51; -5,02</t>
+          <t>-32,65; -4,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 47,68</t>
+          <t>-22,08; 8,52</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49,58</t>
+          <t>47,47</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,33</t>
+          <t>47,27</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>48,48</t>
+          <t>47,47</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 10,35</t>
+          <t>-11,0; 10,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,93; 36,5</t>
+          <t>13,22; 35,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41,04; 57,7</t>
+          <t>38,55; 55,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 14,16</t>
+          <t>-9,01; 13,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,47; 35,19</t>
+          <t>14,03; 35,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,19; 53,87</t>
+          <t>39,3; 54,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 8,73</t>
+          <t>-6,14; 8,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17,64; 32,96</t>
+          <t>17,05; 32,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42,36; 54,09</t>
+          <t>41,32; 53,16</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>124,81%</t>
+          <t>119,49%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>109,95%</t>
+          <t>109,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>117,11%</t>
+          <t>114,65%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 30,91</t>
+          <t>-24,57; 28,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>30,45; 108,25</t>
+          <t>29,24; 105,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88,74; 174,2</t>
+          <t>81,85; 172,2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 38,6</t>
+          <t>-18,32; 35,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>29,19; 92,43</t>
+          <t>28,28; 95,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,64; 148,15</t>
+          <t>78,74; 153,22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 23,08</t>
+          <t>-13,05; 23,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>39,2; 86,72</t>
+          <t>38,8; 89,48</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>90,04; 149,0</t>
+          <t>89,13; 146,13</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18,16</t>
+          <t>17,36</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,77</t>
+          <t>19,71</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18,75</t>
+          <t>18,41</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 15,03</t>
+          <t>-2,49; 14,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5,6; 23,89</t>
+          <t>5,68; 24,52</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9,13; 26,64</t>
+          <t>8,81; 25,75</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 16,25</t>
+          <t>-1,47; 16,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,99; 22,26</t>
+          <t>3,07; 22,53</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,34; 27,87</t>
+          <t>12,21; 27,71</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,32; 12,57</t>
+          <t>0,4; 12,99</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>7,5; 20,04</t>
+          <t>7,31; 20,7</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12,83; 25,06</t>
+          <t>12,3; 24,97</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>65,22%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 76,42</t>
+          <t>-8,82; 72,49</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>19,37; 122,94</t>
+          <t>18,37; 122,46</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>29,76; 132,18</t>
+          <t>30,15; 131,9</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 60,93</t>
+          <t>-3,7; 60,78</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11,14; 82,31</t>
+          <t>7,91; 85,57</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>29,71; 107,73</t>
+          <t>33,31; 105,59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,99; 50,94</t>
+          <t>0,96; 51,68</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>24,56; 79,11</t>
+          <t>22,84; 83,72</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>41,46; 104,02</t>
+          <t>37,64; 103,08</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37,59</t>
+          <t>36,79</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,12</t>
+          <t>30,56</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>25,89</t>
+          <t>33,49</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,24; 14,07</t>
+          <t>2,65; 14,16</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>21,02; 33,7</t>
+          <t>21,63; 33,8</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>31,27; 43,02</t>
+          <t>30,7; 42,2</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,3; 19,17</t>
+          <t>7,66; 18,95</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>16,96; 29,32</t>
+          <t>17,5; 29,6</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 33,12</t>
+          <t>25,26; 35,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,15; 14,94</t>
+          <t>6,95; 14,84</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>21,11; 29,52</t>
+          <t>21,45; 29,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8,48; 35,36</t>
+          <t>29,93; 37,47</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>170,39%</t>
+          <t>166,74%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>117,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>107,29%</t>
+          <t>138,82%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>13,09; 74,49</t>
+          <t>9,91; 71,47</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>84,96; 179,75</t>
+          <t>86,42; 177,91</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>121,4; 227,45</t>
+          <t>120,13; 222,8</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>28,54; 82,0</t>
+          <t>27,53; 81,92</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>59,58; 129,06</t>
+          <t>61,23; 127,77</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-30,25; 131,82</t>
+          <t>85,48; 153,09</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,91; 67,95</t>
+          <t>26,68; 66,66</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>80,89; 135,0</t>
+          <t>80,7; 133,17</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>34,89; 150,14</t>
+          <t>113,12; 172,96</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14,76</t>
+          <t>32,92</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40,21</t>
+          <t>40,47</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>26,03</t>
+          <t>36,82</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-13,45; -2,42</t>
+          <t>-13,71; -2,58</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>10,8; 22,44</t>
+          <t>10,11; 21,71</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 34,35</t>
+          <t>26,89; 38,36</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 2,98</t>
+          <t>-7,24; 3,49</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>14,05; 24,75</t>
+          <t>13,94; 24,83</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>35,33; 45,21</t>
+          <t>35,54; 45,33</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,45; -0,9</t>
+          <t>-8,48; -0,95</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>13,73; 21,8</t>
+          <t>14,04; 22,09</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2,13; 37,81</t>
+          <t>33,06; 40,0</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>119,88%</t>
+          <t>120,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>107,13%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-34,85; -7,33</t>
+          <t>-35,88; -7,83</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>28,17; 71,13</t>
+          <t>25,17; 66,89</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 99,81</t>
+          <t>68,92; 120,99</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 10,09</t>
+          <t>-20,23; 11,33</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>39,41; 80,5</t>
+          <t>37,36; 80,14</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>95,06; 148,7</t>
+          <t>95,44; 150,47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-23,18; -2,58</t>
+          <t>-23,14; -2,77</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>37,78; 67,84</t>
+          <t>37,47; 67,53</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>7,74; 113,63</t>
+          <t>89,06; 125,19</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>23,58</t>
+          <t>27,25</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,43</t>
+          <t>27,74</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>24,0</t>
+          <t>27,49</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,36</t>
+          <t>-3,28; 1,98</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>8,22; 13,7</t>
+          <t>8,47; 13,83</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11,13; 28,62</t>
+          <t>24,49; 30,08</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,27; 5,26</t>
+          <t>0,06; 5,53</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>9,48; 14,79</t>
+          <t>9,36; 14,53</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,99; 28,78</t>
+          <t>25,5; 29,99</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,17</t>
+          <t>-0,64; 3,03</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>9,71; 13,25</t>
+          <t>9,64; 13,39</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>16,28; 27,45</t>
+          <t>25,5; 29,12</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 8,31</t>
+          <t>-10,53; 7,08</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>26,39; 48,5</t>
+          <t>26,93; 48,48</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>34,43; 97,93</t>
+          <t>77,87; 106,62</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>0,93; 17,42</t>
+          <t>0,19; 18,34</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>28,62; 48,68</t>
+          <t>28,56; 48,14</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>42,59; 93,87</t>
+          <t>77,28; 100,24</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 10,48</t>
+          <t>-2,07; 10,29</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>30,89; 44,55</t>
+          <t>30,26; 44,75</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>53,66; 91,33</t>
+          <t>80,87; 98,57</t>
         </is>
       </c>
     </row>
